--- a/sheets/대금율보/검수/아름다운 강산.xlsx
+++ b/sheets/대금율보/검수/아름다운 강산.xlsx
@@ -9408,13 +9408,13 @@
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞淋‹</t>
+㳞淋</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -9470,7 +9470,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潕</t>
         </is>
       </c>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
@@ -9677,7 +9677,7 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="27" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋淋‹
+          <t xml:space="preserve">淋淋
 –汰</t>
         </is>
       </c>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢‹
+          <t xml:space="preserve">汰潢
 –汰</t>
         </is>
       </c>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 –淋</t>
         </is>
       </c>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰汰‹
+          <t xml:space="preserve">汰汰
 –潢</t>
         </is>
       </c>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -10305,7 +10305,7 @@
       <c r="G14" s="28"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞㳞‹
+          <t xml:space="preserve">㳞㳞
 –潢</t>
         </is>
       </c>
@@ -10323,7 +10323,7 @@
       <c r="K14" s="27"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢‹
+          <t xml:space="preserve">汰潢
 –汰</t>
         </is>
       </c>
@@ -10357,7 +10357,7 @@
       <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-–汰‹</t>
+–汰</t>
         </is>
       </c>
       <c r="S14" s="28" t="inlineStr">
@@ -10652,7 +10652,7 @@
       <c r="D19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
-潢‹</t>
+潢</t>
         </is>
       </c>
       <c r="E19" s="22"/>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -10815,7 +10815,7 @@
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋湳‹
+          <t xml:space="preserve">淋湳
 –潕</t>
         </is>
       </c>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
@@ -10942,7 +10942,7 @@
       <c r="H22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="R22" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢‹
+          <t xml:space="preserve">汰潢
 –汰</t>
         </is>
       </c>
@@ -11034,7 +11034,7 @@
       <c r="F23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G23" s="22"/>
@@ -11103,7 +11103,7 @@
       <c r="F24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G24" s="25"/>
@@ -11260,7 +11260,7 @@
       <c r="O26" s="27"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 –淋</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/아름다운 강산.xlsx
+++ b/sheets/대금율보/검수/아름다운 강산.xlsx
@@ -9334,32 +9334,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="U5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -9872,7 +9872,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="U9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="U14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -10489,7 +10489,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.43" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="U17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.43" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="U18" s="27"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="U20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="U21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="U22" s="27"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="63.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="63.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="U24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="63.43" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="25"/>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="U25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="63.43" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="27"/>
@@ -11283,10 +11283,10 @@
       </c>
       <c r="U26" s="27"/>
     </row>
-    <row r="27">
+    <row r="27" ht="6.0" customHeight="true">
       <c r="A27" s="0"/>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28" ht="85.11" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
       <c r="T28" s="20"/>
       <c r="U28" s="20"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="63.43" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -11341,7 +11341,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="63.43" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="25"/>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="63.43" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="25"/>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="63.43" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="27"/>
@@ -11437,7 +11437,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="63.43" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -11469,7 +11469,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="63.43" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="25"/>
@@ -11492,7 +11492,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="25"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="63.43" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="25"/>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="U35" s="25"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="63.43" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="27"/>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="U36" s="27"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="63.43" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="63.43" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="25"/>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="63.43" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="25"/>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="63.43" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="27"/>
@@ -11670,7 +11670,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="63.43" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="22"/>
@@ -11701,7 +11701,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="63.43" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="25"/>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="U42" s="25"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="63.43" customHeight="true">
       <c r="A43" s="0"/>
       <c r="B43" s="21"/>
       <c r="C43" s="25"/>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="U43" s="25"/>
     </row>
-    <row r="44" ht="56" customHeight="1">
+    <row r="44" ht="63.43" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="21"/>
       <c r="C44" s="27"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="U44" s="27"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="63.43" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="63.43" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="25"/>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="U46" s="25"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="63.43" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="25"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="U47" s="25"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="63.43" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="27"/>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="U48" s="27"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="63.43" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="63.43" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="25"/>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="U50" s="25"/>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="63.43" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="25"/>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="U51" s="25"/>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="63.43" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="27"/>
@@ -12007,7 +12007,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="26" max="16383" man="1"/>
   </rowBreaks>
